--- a/AAII_Financials/Quarterly/LGGNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGGNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="92">
   <si>
     <t>LGGNY</t>
   </si>
@@ -656,88 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="19" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -780,23 +786,29 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3">
         <v>41481100</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -839,23 +851,29 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3">
         <v>229100</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -898,23 +916,29 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3">
         <v>41252100</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -936,8 +960,10 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -995,8 +1021,14 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1054,8 +1086,14 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1113,8 +1151,14 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1157,14 +1201,14 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
+      <c r="S15" s="3">
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
@@ -1172,8 +1216,14 @@
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1192,8 +1242,10 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1236,23 +1288,29 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3">
         <v>40000600</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1295,23 +1353,29 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3">
         <v>1480500</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1333,8 +1397,10 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1377,14 +1443,14 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
@@ -1392,8 +1458,14 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1451,8 +1523,14 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1495,14 +1573,14 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
@@ -1510,8 +1588,14 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1554,23 +1638,29 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3">
         <v>1480500</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1613,23 +1703,29 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3">
         <v>166300</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1687,8 +1783,14 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1731,23 +1833,29 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3">
         <v>1314200</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1790,23 +1898,29 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3">
         <v>1338500</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1864,8 +1978,14 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1908,23 +2028,29 @@
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S29" s="3">
         <v>346800</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1982,8 +2108,14 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2041,8 +2173,14 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2085,14 +2223,14 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
@@ -2100,8 +2238,14 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2144,23 +2288,29 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3">
         <v>1685200</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2218,8 +2368,14 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2262,87 +2418,99 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3">
         <v>1685200</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2364,8 +2532,10 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2387,117 +2557,125 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19261000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>19169300</v>
+      </c>
+      <c r="F41" s="3">
         <v>23012100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>22983000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>16927000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>15962700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>20853300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>22325400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>19975500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>19962600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>26128500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>25032300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>18473500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>17984200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>43115900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>23058600</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>688756400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>687886100</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>606605200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>649427700</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>587601300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>562948800</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>527884800</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
+      <c r="S42" s="3">
+        <v>0</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
@@ -2505,117 +2683,129 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13659300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>13594300</v>
+      </c>
+      <c r="F43" s="3">
         <v>6908500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>6899700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>12760700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>12033700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>9125300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>9769500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>17260900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>17249700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>8753200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>8386000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>16304300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>15872400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>12475500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>12065400</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>517400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>515000</v>
+      </c>
+      <c r="F44" s="3">
         <v>531600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>531000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>935700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>882400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>664800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>711700</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3">
         <v>2460900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>2357700</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P44" s="3">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R44" s="3">
         <v>2377300</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
+      <c r="S44" s="3">
+        <v>0</v>
       </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
@@ -2623,58 +2813,64 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>73778700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>73427500</v>
+      </c>
+      <c r="F45" s="3">
         <v>29686400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>29648900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>99241000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>93587800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>12114900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>12970100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>65233100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>65191100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>10170900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>9744200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>66268100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>64512800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>6479900</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
+      <c r="S45" s="3">
+        <v>0</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
@@ -2682,58 +2878,64 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>107216400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>106706000</v>
+      </c>
+      <c r="F46" s="3">
         <v>749413200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>748466300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>129864400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>122466700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>649832900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>695707000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>102469400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>102403400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>635619300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>608952200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>101045900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>98369500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>592796000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
+      <c r="S46" s="3">
+        <v>0</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
@@ -2741,185 +2943,209 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>675126700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>671912900</v>
+      </c>
+      <c r="F47" s="3">
         <v>13916600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>13899000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>603811500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>569415600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>14721400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>15760600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>538759200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>538412200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>13591000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>13020800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>504085600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>490733900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>10697000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>674327600</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>626200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>623300</v>
+      </c>
+      <c r="F48" s="3">
         <v>446800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>446300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>474000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>447000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>494500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>529400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>539600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>539300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>551500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>528400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>460000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>447800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>392800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>11195300</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>483000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>480700</v>
+      </c>
+      <c r="F49" s="3">
         <v>531600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>531000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>534300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>503900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>600900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>643300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>681200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>680700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>700600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>671200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>673500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>655700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>616900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>508000</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2977,8 +3203,14 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3036,67 +3268,79 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>15546000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>15472000</v>
+      </c>
+      <c r="F52" s="3">
         <v>16965000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>16943600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>13903300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>13111300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>13321700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>14262200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>11707800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>11700200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>12359300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>11840700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>11725600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>11415000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>12195900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>6400</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3154,67 +3398,79 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>813853000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>809978800</v>
+      </c>
+      <c r="F54" s="3">
         <v>783671600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>782681400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>763152500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>719679800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>681256200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>729348600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>665410000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>664981400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>665021400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>637120800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>635105700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>618283600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>618434800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>730100700</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3236,8 +3492,10 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3259,58 +3517,60 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>6600</v>
+      </c>
+      <c r="F57" s="3">
         <v>2700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>9600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>9000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>212800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>227900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>179500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>179300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>280200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>268500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>175400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>170700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>62700</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
+      <c r="S57" s="3">
+        <v>0</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
@@ -3318,176 +3578,194 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>28667900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>28531400</v>
+      </c>
+      <c r="F58" s="3">
         <v>70510100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>70421000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>30659000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>28912500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>80349800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>86022000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>28049800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>28031800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>75735000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>72557500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>36023200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>35069000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>83805000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>43500</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>83720300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>83321800</v>
+      </c>
+      <c r="F59" s="3">
         <v>98720100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>98595300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>98817600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>93188500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>67299700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>72050700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>63322300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>63281500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>58429700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>55978300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>69859300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>68009000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>60159000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>622512400</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>112394900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>111859800</v>
+      </c>
+      <c r="F60" s="3">
         <v>169913900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>169699200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>129486200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>122110100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>148609700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>159100700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>91551600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>91492600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>135092000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>129424300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>106057900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>103248700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>144649700</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
+      <c r="S60" s="3">
+        <v>0</v>
       </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
@@ -3495,126 +3773,144 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6576900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6545600</v>
+      </c>
+      <c r="F61" s="3">
         <v>6577400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>6569100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>6454300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>6086600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>9712400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>10398100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>7695200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>7690300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>7901100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>7569600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>7052900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>6866100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>6810000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>7439700</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>691257800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>687967200</v>
+      </c>
+      <c r="F62" s="3">
         <v>603935400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>603172300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>623886800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>588347400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>518276900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>554864000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>560976700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>560615300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>515743600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>494105900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>513570800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>499967800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>459300000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>264900</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3672,8 +3968,14 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3731,8 +4033,14 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3790,67 +4098,79 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>810305200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>806447900</v>
+      </c>
+      <c r="F66" s="3">
         <v>780559900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>779573600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>759827400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>716544100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>676860700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>724642800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>660463600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>660038100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>658927800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>631282800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>628684300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>612032400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>611768200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>717308400</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3872,8 +4192,10 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3931,8 +4253,14 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3990,8 +4318,14 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4037,11 +4371,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S70" s="3" t="s">
-        <v>3</v>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
       </c>
       <c r="T70" s="3" t="s">
         <v>3</v>
@@ -4049,8 +4383,14 @@
       <c r="U70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4108,67 +4448,79 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2814100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2800700</v>
+      </c>
+      <c r="F72" s="3">
         <v>695800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>694900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>850800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>802300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>2145800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>2297300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>2650200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2648500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>3786900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>3628000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>4084300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>3976100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>4466500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>10674500</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4226,8 +4578,14 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4285,8 +4643,14 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4344,67 +4708,79 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3517300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3500600</v>
+      </c>
+      <c r="F76" s="3">
         <v>3072700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3068800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3303200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3115000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>4441800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4755400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5002100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4998900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>6147100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>5889200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>6465800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>6294500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>6701600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>12792300</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4462,72 +4838,84 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4570,23 +4958,29 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3">
         <v>1685200</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4608,58 +5002,60 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3">
         <v>30700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>32800</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3">
         <v>30600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>29300</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
         <v>33700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>31200</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3">
         <v>35900</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
+      <c r="S83" s="3">
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
@@ -4667,8 +5063,14 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4726,8 +5128,14 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4785,8 +5193,14 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4844,8 +5258,14 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4903,8 +5323,14 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4962,56 +5388,62 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2012700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2003200</v>
+      </c>
+      <c r="F89" s="3">
         <v>3539000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>3534600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-487100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-459300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-487000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-521400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-2317800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-2316300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>3811100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>3651200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-12852800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-12512400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>6926300</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5021,8 +5453,14 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5044,67 +5482,75 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-114800</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-114200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-12800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-12800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-21900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-20700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-41300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-44200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-18300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-18300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-42000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-40300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-108700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-105800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-76500</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5162,8 +5608,14 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5221,56 +5673,62 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>302500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>301100</v>
+      </c>
+      <c r="F94" s="3">
         <v>147400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>147200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-33600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-31700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>209100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>223800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-60000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-60000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-136900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-131200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-131500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-128000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-102400</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5280,8 +5738,14 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5303,56 +5767,58 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>597100</v>
+      </c>
+      <c r="E96" s="3">
+        <v>594200</v>
+      </c>
+      <c r="F96" s="3">
         <v>244300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>244000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>624700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>589200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>231600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>248000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>561100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>560800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>226100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>216600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>536900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>522700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>203600</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -5362,8 +5828,14 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5421,8 +5893,14 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5480,8 +5958,14 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5539,56 +6023,62 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-824600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-820700</v>
+      </c>
+      <c r="F100" s="3">
         <v>-199900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-199600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1803000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1700300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>800000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>856500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-598400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-598000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>137600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>131800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-490500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-477500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-204200</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5598,56 +6088,62 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-69200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-65200</v>
+      </c>
+      <c r="F101" s="3">
         <v>10600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>11400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>1900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>1900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-5700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-5500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-25400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-24700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>13300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>12300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>42500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>46000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>10800</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5657,56 +6153,62 @@
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2534800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-2522800</v>
+      </c>
+      <c r="F102" s="3">
         <v>3481800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>3477400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-2392800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-2256500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>532700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>570300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-2974300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-2972400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>3806000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>3646300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-13500300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-13142700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>6632900</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5714,6 +6216,12 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
